--- a/backlog/backlog.xlsx
+++ b/backlog/backlog.xlsx
@@ -1,31 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Payam\Documents\GitHub\payameno\backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47B06C1-4984-46B4-A901-03BF0107B0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB53521-ED6F-4F9D-B940-F9E1EC6378C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="backlog" sheetId="1" r:id="rId1"/>
+    <sheet name="ترم اول 404" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="46">
   <si>
     <t>ردیف</t>
   </si>
@@ -123,9 +133,6 @@
     <t xml:space="preserve">ساعت </t>
   </si>
   <si>
-    <t>40-08-20</t>
-  </si>
-  <si>
     <t>اصلاح ساختار دیتابیس  - فایل ایجاد دیتابیس</t>
   </si>
   <si>
@@ -133,13 +140,46 @@
   </si>
   <si>
     <t>افزودن درس های رشته  و انتقال از درس به درس</t>
+  </si>
+  <si>
+    <t>404-08-20</t>
+  </si>
+  <si>
+    <t>404-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ایجاد زبانه رشته های درس </t>
+  </si>
+  <si>
+    <t>404-08-26</t>
+  </si>
+  <si>
+    <t>قابلیت انتقال درس از یک رشته به رشته دیگر</t>
+  </si>
+  <si>
+    <t>404-09-10</t>
+  </si>
+  <si>
+    <t>دریافت  انتخاب واحد از سیدا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عنوان </t>
+  </si>
+  <si>
+    <t>ساعت</t>
+  </si>
+  <si>
+    <t>405-01-24</t>
+  </si>
+  <si>
+    <t>اصلاح کارت ورود به جلسه بر اساس مقطع</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +194,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="B Nazanin"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="B Nazanin"/>
+      <charset val="178"/>
     </font>
   </fonts>
   <fills count="3">
@@ -170,7 +223,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -178,11 +231,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -192,6 +260,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -255,8 +335,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A7CE2822-90C9-4845-9557-7296864ED1A3}" name="Table1" displayName="Table1" ref="A1:G17" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G17" xr:uid="{A7CE2822-90C9-4845-9557-7296864ED1A3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A7CE2822-90C9-4845-9557-7296864ED1A3}" name="Table1" displayName="Table1" ref="A1:G21" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G21" xr:uid="{A7CE2822-90C9-4845-9557-7296864ED1A3}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="باز"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{5CCAB5B4-B8F6-4E04-8E8E-709BF9E424BB}" name="ردیف" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{0E71090F-41A5-4A44-9408-17E26EA70184}" name="تاریخ" dataDxfId="5"/>
@@ -533,11 +619,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="14.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="39.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="2"/>
@@ -569,7 +655,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -592,7 +678,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -632,7 +718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -652,7 +738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -672,7 +758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -692,7 +778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -715,7 +801,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -726,16 +812,16 @@
         <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -755,7 +841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -775,7 +861,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -795,7 +881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -818,7 +904,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -858,7 +944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -866,7 +952,7 @@
         <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -878,27 +964,104 @@
         <v>8</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="2">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2">
-        <v>2</v>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -907,4 +1070,281 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195F5AB2-D40A-4BB6-8877-A1C98E977D19}">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="44.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="4">
+        <f>SUM(D2:D18)</f>
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/backlog/backlog.xlsx
+++ b/backlog/backlog.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Payam\Documents\GitHub\payameno\backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB53521-ED6F-4F9D-B940-F9E1EC6378C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B42C9B6-55A6-4B73-9099-788D225E3E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="backlog" sheetId="1" r:id="rId1"/>
-    <sheet name="ترم اول 404" sheetId="2" r:id="rId2"/>
+    <sheet name="ترم دوم 404-405" sheetId="3" r:id="rId2"/>
+    <sheet name="ترم اول 404" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
   <si>
     <t>ردیف</t>
   </si>
@@ -173,13 +174,25 @@
   </si>
   <si>
     <t>اصلاح کارت ورود به جلسه بر اساس مقطع</t>
+  </si>
+  <si>
+    <t>اصلاح ساختار دیتابیس گزارش  های  و فرم ها</t>
+  </si>
+  <si>
+    <t>گزارش اقدامات توسعه نرم افزار مالی  ترم دوم405-405</t>
+  </si>
+  <si>
+    <t>ساعت کارکرد</t>
+  </si>
+  <si>
+    <t>تاریخ درخواست</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +217,13 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="B Nazanin"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="B Nazanin"/>
       <charset val="178"/>
@@ -250,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -272,6 +292,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -335,8 +358,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A7CE2822-90C9-4845-9557-7296864ED1A3}" name="Table1" displayName="Table1" ref="A1:G21" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G21" xr:uid="{A7CE2822-90C9-4845-9557-7296864ED1A3}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A7CE2822-90C9-4845-9557-7296864ED1A3}" name="Table1" displayName="Table1" ref="A1:G23" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G23" xr:uid="{A7CE2822-90C9-4845-9557-7296864ED1A3}">
     <filterColumn colId="3">
       <filters>
         <filter val="باز"/>
@@ -619,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
@@ -1055,13 +1078,30 @@
         <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
       </c>
       <c r="F21" s="2">
         <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1073,6 +1113,71 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{901D5147-02D5-48DF-8627-B4656524BE62}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="24" x14ac:dyDescent="0.25">
+      <c r="C5" s="4">
+        <f>SUM(C3:C4)</f>
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195F5AB2-D40A-4BB6-8877-A1C98E977D19}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
